--- a/Bonds/bond_report.xlsx
+++ b/Bonds/bond_report.xlsx
@@ -413,56 +413,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>ISIN</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SellPrice</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Депозиты Банка</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Фио</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>Рейтинг</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Кол-во обл</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Средняя цена</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ТКД</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Дата оферты</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Спекуляции</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Доход</t>
         </is>
@@ -471,2628 +486,2979 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Металлоинвест ХК-002P-04 ISIN: RU000A10E7W8 AA /AAA (АКРА/НКР) Ориентир купона: ФИНАЛ = КС+1.85 (было КС + не более 2%) каждые 30 дней Без оферт 4 года до погашения: 08.02.2030 Сбор заявок 03.02.26 Начало торгов - 9 февраля</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>RU000A10E7W8</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>99.98</v>
-      </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>АА</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
         <v>100</v>
       </c>
-      <c r="F2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
         <v>17.35</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>-0.01999999999999602</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>МФК ЛАЙМ-ЗАЙМ 001P-05 Ставка купона: ФИНАЛ 23,5% (YTM 26,21%). Борьба за уровень купона не осуществлялась ввиду режима сбора заявок Z0 (размещение в день сбора) Срок обращения: 5 лет Купон: ежемесячный Рейтинг: ВВ+ Объём размещения: 2 миллиарда Амортизация: 12,5% одновременно с выплатой купонного дохода 18, 24, 30, 36, 42, 48, 54 и 60 Оферта: 29.02.28 сall-опцион через 2 и 3 года Сбор заявок: 11 марта Дата размещения: 11 марта 2026 года. Для квалов. Погашение 13.02.31, если не будет оферт</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>RU000A10EHB3</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>101.41</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
         <v>103.5</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>ВВ+</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
         <v>136</v>
       </c>
-      <c r="F3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
         <v>23.5</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>29 февр. 2028 г.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>1.409999999999997</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>A101-50-001P-02 Номинал: 1000 Р Объем: 3 млрд Р (на оба выпуска) Погашение: через 2 года Купон: ФИНАЛ 17% (18% (YTM 19,56%)) Выплаты: 12 раз в год Амортизация: Нет Оферта: Нет Рейтинг: A+(RU) AKPA / ruA+ Эксперт PA / A+.ru HKP Размещение: 26 декабря 2025 года</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>RU000A10DZU7</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>101.85</v>
-      </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>А+</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="H4" t="n">
         <v>900</v>
       </c>
-      <c r="F4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
         <v>17</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>1.849999999999994</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>A101-50-001P-03 Номинал: 1000 Р Погашение: через 2 года Купон: ФИНАЛ КС +400 (КС +450 б.п.) Выплаты: 12 раз в год Амортизация: Нет Оферта: Нет Рейтинг: A+(RU) AKPA / ruA+ Эксперт PA / A+.ru HKP Только для квалов: Да Сбор заявок: 24 декабря 2025 года Размещение: 26 декабря 2025 года</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>RU000A10DZT9</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>А+</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="H5" t="n">
         <v>400</v>
       </c>
-      <c r="F5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
         <v>19.5</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>АЛРОСА 001P-02. RU000A109SH2. Взял с рынка по цене 1000.6 руб. Купон ежм КС+1.14%. (Доходность 19.21% при кс=17%). ОСТАЛОСЬ 5 МЕС ДО ПОГАШЕНИЯ.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>RU000A109SH2</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>100</v>
-      </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="H6" t="n">
         <v>30</v>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>1000.6</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>16.63</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>-0.06000000000000227</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>АЛРОСА 001Р-01 RU000A109L49 (взял с рынка по 99.82%) КС+1.2% ежм на 3 не полных года без оферты и амортизации</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>RU000A109L49</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>99.7</v>
-      </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="H7" t="n">
         <v>100</v>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>998.2</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>16.73</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>-0.1200000000000045</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>ПГК 003Р-02 (фикс) RU000A10DSL1 - Дата ДОПОЛНИТЕЛЬНОГО размещения: 05.02.26 Рейтинг: АА, прогноз «стабильный» (Эксперт РА) Купон ежемесячный: фикс ФИНАЛ= 15.95% Срок: 3,1 года фикс Амортизация: нет ОФЕРТА PUT: 29.03.29 Номинал: 1000 руб. !!! Внимание !!! ОФЕРТА PUT: 29.03.29 Можно ПРОДАТЬ после 05.02.29 с ЛДВ. Погашение: 16.11.30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>RU000A10DSL1</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>101.38</v>
-      </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>АА</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="H8" t="n">
         <v>200</v>
       </c>
-      <c r="F8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
         <v>15.95</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>29 мар. 2029 г.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>1.379999999999995</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>АПРИ-002P-13 RU000A10E5C4 Рейтинг: BBB- (HPA, прогноз «Стабильный») Купон: финал 24.5% (ежемесячный) (YTM 27,45%) Срок обращения: 3.5 года Объем: 1 млрд. Р Амортизация: да (33, 36, 39, 42 по 25%) Оферта: нет Номинал: 1000 Р Сбор заявок 20 января 11:00-15:00 размещение 23 января Погашение 06.07.29</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>RU000A10E5C4</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>101.78</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
         <v>103.5</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>ВВВ-</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="H9" t="n">
         <v>300</v>
       </c>
-      <c r="F9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
         <v>24.5</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>1.780000000000001</v>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>• АФК Система 002P-05 $RU000A10CU55 Рейтинг: АА- - Купон: ключевая ставка ЦБ+3,5% - Частота выплат: 12 раз в ГОД - КУПИЛ с рынка по цене цена: 994,5Р - Дата погашения: 16.09.2027</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>RU000A10CU55</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>98.90000000000001</v>
-      </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>АА-</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="H10" t="n">
         <v>100</v>
       </c>
-      <c r="F10" t="n">
+      <c r="I10" t="n">
         <v>994.5</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>19.105</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>-0.5499999999999972</v>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>АЭРОФЬЮЭЛЗ Аэрфью-003Р-01 RU000A10E4Y1 Рейтинг: А (НКР, прогноз «Стабильный») Купон: Финал 20.0% (квартальный) Срок обращения: 2.5 года Объем: 1 млрд. Р Амортизация: нет Оферта: нет Номинал: 1000 Р Сбор заявок 20 января 11:00-16:00 размещение 23 января 2025 года Погашение 23.07.28</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>RU000A10E4Y1</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>104.27</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
         <v>103.5</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>А</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="H11" t="n">
         <v>149</v>
       </c>
-      <c r="F11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
         <v>20</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>4.269999999999996</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Акции ВК RU000A106YF0 (взамен на иностранные бумаги)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>RU000A106YF0</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
         <v>220</v>
       </c>
-      <c r="F12" t="n">
+      <c r="I12" t="n">
         <v>1691.2</v>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Акции Лента RU000A102S15 (взамен на иностранные бумаги)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>RU000A102S15</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
         <v>244</v>
       </c>
-      <c r="F13" t="n">
+      <c r="I13" t="n">
         <v>1195.2</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Атомэнергопром Атомэнп-001P-10 Рейтинг: ААА (АКРА, прогноз «Стабильный») Купон: ФИНАЛ 15.15% КБД (5.5 лет)+150 б.п.= 15.15 (квартальный) Срок обращения: 5.5 лет Объем: 25 млрд. Р Амортизация: нет Оферта: нет Номинал: 1000 Р Размещение 24 декабря</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>RU000A10DYG9</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>103.49</v>
-      </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="H14" t="n">
         <v>300</v>
       </c>
-      <c r="F14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J14" t="n">
         <v>15.15</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>3.489999999999995</v>
-      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Атомэнергопром (001P-11) - Купон: ФИНАЛ = 14.7%. Фиксированный, Было: КБД (3 года 9 мес.) + премия до 150 б.п. (ожидаемо ~15,4%, YTM до 16,2%) Ежеквартально - Погашение: 07.12.2029 (срок 3 года 9 месяцев) - Рейтинг: ruAAA (Эксперт РА) - Амортизация: Нет Оферта: Нет Объем выпуска: 30 млрд руб. - Прием заявок: С 11 марта 2026, размещение 13 марта 2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>RU000A10EJQ7</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>100.59</v>
-      </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="H15" t="n">
         <v>500</v>
       </c>
-      <c r="F15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J15" t="n">
         <v>14.7</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>0.5900000000000034</v>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Облигации Атомэнергопром 001Р-09 RU000A10DPS2 с фиксированным купоном ФИНАЛ 15.10 (было 15.0-16.4%) на 5 лет без оферты и амортизации. Выплата каждый квартал в марте, июне, сентябре и декабре Погашение 29.05.31</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>RU000A10DPS2</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>103.11</v>
-      </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="H16" t="n">
         <v>500</v>
       </c>
-      <c r="F16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J16" t="n">
         <v>15.1</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>3.109999999999999</v>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Балтийский лизинг Б0-П16 RU000A10BJX9 на 2 года 11 месяцев. Первичное размещение под 22.5-23%. Выплата каждые 30 дней</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>RU000A10BJX9</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>103.1</v>
-      </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>АА- Стабильный</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="H17" t="n">
         <v>200</v>
       </c>
-      <c r="F17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J17" t="n">
         <v>22.25</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>3.099999999999994</v>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Балтийский лизинг Б0-П19 АА- на 3 года. Первичное размещение под 17%. Выплата каждые 30 дней Оферта CALL 27.08.28. Дата погашения 21.08.35</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>RU000A10СС32</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>АА- Стабильный</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="H18" t="n">
         <v>500</v>
       </c>
-      <c r="F18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J18" t="n">
         <v>17</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>27 авг. 2028 г.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>ВТБ Лизинг 001Р-МБ-03 АА RU000A10CQE2 на 3 года. Первичное размещение под 15.5%. Выплата каждые 30 дней. Амортизация каждые 3 мес по 8.3%. Оферты нет</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>RU000A10CQE2</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>100.45</v>
-      </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>АА Стабильный</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="H19" t="n">
         <v>160</v>
       </c>
-      <c r="F19" t="n">
+      <c r="I19" t="n">
         <v>834</v>
       </c>
-      <c r="G19" t="n">
+      <c r="J19" t="n">
         <v>18.585</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>17.05</v>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>ВЭБ-002P-54B Купон: 7.50% (ежемесячный) Срок обращения: 5 лет Объем: 300 млн. $ Амортизация: нет Оферта: нет Номинал: 1000 $</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>RU000A10CTX6</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>99.62269999999999</v>
-      </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>ААА (АКРА, прогноз Стабильный)</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="H20" t="n">
         <v>5</v>
       </c>
-      <c r="F20" t="n">
+      <c r="I20" t="n">
         <v>83606.89999999999</v>
       </c>
-      <c r="G20" t="n">
+      <c r="J20" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>-8261.067299999999</v>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>ВЭБ-РФ 002P-36 ● ISIN: RU000A105YH8 ● Купон: RUONIA+170 б.п. . на 5 лет ● Выплат в год: 4 (март, июнь, сентябрь, декабрь) ● Погашение: 18.09.2030 ● Рейтинг: ААA от АКРА и Эксперт НА Без оферты и амортизации Купил 06.11.25 с рынка по цене 98.81%</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>RU000A105YH8</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>98.09999999999999</v>
-      </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="H21" t="n">
         <v>50</v>
       </c>
-      <c r="F21" t="n">
+      <c r="I21" t="n">
         <v>988.1</v>
       </c>
-      <c r="G21" t="n">
+      <c r="J21" t="n">
         <v>17.407</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>-0.710000000000008</v>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>ГК Азот-001P-02 Рейтинг: А+ (Эксперт РА, прогноз «Стабильный») Купон: ФИНАЛ 16.5 (было до 17.25%) (ежемесячный) Срок обращения: 5 лет Объем: 5 млрд. Р Амортизация: нет !!!!!!!!!!!!!!!!!! Оферта: да (Пут через 2 года, 720 дней = 10.02.28) !!!!!!!!!!!!!!!!! Номинал: 1000 Р Сбор заявок 17 февраля 11:00-15:00 размещение 20 февраля Погашение 20.02.31</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>RU000A10EA40</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>101.86</v>
-      </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>А+</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="H22" t="n">
         <v>417</v>
       </c>
-      <c r="F22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="I22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J22" t="n">
         <v>16.5</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>10 февр. 2028 г.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="n">
-        <v>1.859999999999999</v>
-      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>ГК ПИОНЕР 002P-03 А (АКРА, Эксперт, НКР) Только для квалов Ориентир купона: ФИНАЛ КС + 4.5% (было не более 4,5%) [30 дней) Без оферт 3 года до погашения Начало торгов - 11 марта</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>RU000A10EHJ6</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>100.3</v>
-      </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>А</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="H23" t="n">
         <v>300</v>
       </c>
-      <c r="F23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
         <v>20</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
-        <v>0.2999999999999972</v>
-      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>ГТЛК 001Р-22 - Купон: финал = 9.5% (было до 9,50%). Купон=0.78$ Номинал 100$ Фиксированный с привязкой к USD. Выплаты в рублях по курсу ЦБ. - Выплаты: Ежемесячно - Погашение: 3,5 года - Рейтинг: АА- (стабильный, АКРА и Эксперт РА) - Амортизация: По 50% номинала на 39-й и 43-й купоны - Оферта: Нет - Объем выпуска: Не менее 100 млн USD - Прием заявок: До 12 февраля 2026 г. Размещение 17.02.26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>RU000A10EAM5</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>103.1956</v>
-      </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>АА- стабильный</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="H24" t="n">
         <v>23</v>
       </c>
-      <c r="F24" t="n">
+      <c r="I24" t="n">
         <v>7662.01</v>
       </c>
-      <c r="G24" t="n">
+      <c r="J24" t="n">
         <v>1.24</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
-        <v>-663.0054</v>
-      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RUO00A10D2Q2</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>Газпром капитал БО-003Р-06 на 2 года под 17.5-18.5% (финал=КС+1.4) ежм без оферты и амортизации</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>RU000A10D2Q2</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="H25" t="n">
         <v>500</v>
       </c>
-      <c r="F25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="I25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J25" t="n">
         <v>16.9</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Газпром нефть 005P-01R USD RU000A10D483 под 5.5-7.75% (ФИНАЛ 7.5%) ежм на 3.5 года без оферты и амортизации. Номинал 1000 USD</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>RU000A10D483</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="H26" t="n">
         <v>9</v>
       </c>
-      <c r="F26" t="n">
+      <c r="I26" t="n">
         <v>78839</v>
       </c>
-      <c r="G26" t="n">
+      <c r="J26" t="n">
         <v>0.095</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Газпром нефть 005P-02R ГaзпpHeф-005P-02R RU000A10DA66 под ФИНАЛ= (кс + 150) ежм на 3.5 года без оферты и амортизации. Номинал 1000 руб</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>RU000A10DA66</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>99.81999999999999</v>
-      </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="H27" t="n">
         <v>400</v>
       </c>
-      <c r="F27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="I27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J27" t="n">
         <v>17</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>-0.1800000000000068</v>
-      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Газпром нефть БО 003P-14R ISIN: RU000A10BK09 • Купон: КС+200 б.п. • Текущая цена: 100,98% CY: 18,32% • Выплат в год: 12 ► Погашение: 27.04.2027 • Рейтинг: ААА от АКРА и Эксперт НА Взял с рынка по цене 100.82%</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>RU000A10BK09</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>100.64</v>
-      </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="H28" t="n">
         <v>34</v>
       </c>
-      <c r="F28" t="n">
+      <c r="I28" t="n">
         <v>1008.75</v>
       </c>
-      <c r="G28" t="n">
+      <c r="J28" t="n">
         <v>17.348</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>-0.2349999999999994</v>
-      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Глоракс 1Р5 Рейтинг: BBB (RU) от АКРА (август 2025), BBB+ от НКР (апрель 2025) на 3 года 5 месяцев. Номинал: 1000 Р Объем: не менее 3 млдр.Р Купонная доходность: Финал= 20.5%. (Было до 21%) ежемесячно, что соответствует Доходности к погашению до 23,1% Амортизация: нет Оферта: нет Сбор заявок: 23 января размещения: 28 января Дата погашения: 11 июля 2029</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>RU000A10E655</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>103.4</v>
-      </c>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
         <v>104.5</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>ВВВ</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="H29" t="n">
         <v>330</v>
       </c>
-      <c r="F29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="I29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J29" t="n">
         <v>20.5</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
-        <v>3.400000000000006</v>
-      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Группа ЛСР БО 001Р- 11. На 3 года под 16.25-17.25 ежм (ФИНАЛ 16%). Без оферты. Амортизация по 30% на 24 и 30 купонах.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>RU000A10CKY3</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>100.2</v>
-      </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>А Стабильный</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="H30" t="n">
         <v>159</v>
       </c>
-      <c r="F30" t="n">
+      <c r="I30" t="n">
         <v>996.0599999999999</v>
       </c>
-      <c r="G30" t="n">
+      <c r="J30" t="n">
         <v>16.063</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>0.5940000000000083</v>
-      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Дельтализинг 001Р-03 RU000A10DHT7 - Купон: 17.15% - Выплаты: ежемесячно - Погашение: через 3 года - Рейтинг: АА- - Амортизация: 4% номинала с 12-го купона ежемесячно - Оферта: нет</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>RU000A10DHT7</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>102.23</v>
-      </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>АА-</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="H31" t="n">
         <v>200</v>
       </c>
-      <c r="F31" t="n">
+      <c r="I31" t="n">
         <v>996.9</v>
       </c>
-      <c r="G31" t="n">
+      <c r="J31" t="n">
         <v>17.203</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
-        <v>2.540000000000006</v>
-      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Денежный рынок Альфа-Капитал. АКММ. Ставка около КС РФ. Портфель ..7040</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>RU000A104X08</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
         <v>498</v>
       </c>
-      <c r="F32" t="n">
+      <c r="I32" t="n">
         <v>165.55</v>
       </c>
-      <c r="G32" t="n">
+      <c r="J32" t="n">
         <v>93.627</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Денежный рынок. TMON</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>RU000A106DL2</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="n">
         <v>336</v>
       </c>
-      <c r="F33" t="n">
+      <c r="I33" t="n">
         <v>153.13</v>
       </c>
-      <c r="G33" t="n">
+      <c r="J33" t="n">
         <v>104.486</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Департамент финансов ЯНАО. RU000A10DMS9 Купон: ФИНАЛ КС+150 (было до КС+200 б.п.) Выплаты: 12 раз в год Срок: 3 года Оферта: нет • Рейтинг: ААА от АКРА Амортизация: 50% от номинала в дату выплаты 24 купона Сбор заявок - 27 ноября, размещение - 2 декабря 2025.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>RU000A10DMS9</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>100.43</v>
-      </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="H34" t="n">
         <v>100</v>
       </c>
-      <c r="F34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J34" t="n">
         <v>17</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
-        <v>0.4300000000000068</v>
-      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Инарктика 002P-04: • Рейтинг: A+(RU), прогноз «Стабильный» (АКРА) Номинал: 1000Р Срок обращения: 3 года • Купон: ФИНАЛ =15.75 (было не выше 18% годовых) • Периодичность выплат: ежемесячно • Амортизация: отсутствует Оферта: нет</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>RU000A10DHX9</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>103.07</v>
-      </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>А+</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="H35" t="n">
         <v>1</v>
       </c>
-      <c r="F35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="I35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J35" t="n">
         <v>15.75</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>3.069999999999993</v>
-      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Инарктика 002P-05: • Рейтинг: A+(RU), прогноз «Стабильный» (АКРА) Номинал: 1000Р Срок обращения: 3 года • Купон: ФИНАЛ КС+290 (было не выше КС+300 б. п.) годовых • Периодичность выплат: ежемесячно • Амортизация: отсутствует Оферта: нет</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>RU000A10DHV3</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>100.5</v>
-      </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>А+</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="H36" t="n">
         <v>170</v>
       </c>
-      <c r="F36" t="n">
+      <c r="I36" t="n">
         <v>1001.1</v>
       </c>
-      <c r="G36" t="n">
+      <c r="J36" t="n">
         <v>18.38</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>0.3900000000000006</v>
-      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Кредитный Поток 3.0 RU000A10DBM5— это облигации, обеспеченные портфелем кредитных карт Т-Банка. Под 17,3% фикс ЕЖМ каждого 24 числа месяца на 25 месяцев. Оферта Call 24.12.27 на весь объём. При отсутствии оферты начнётся амортизация до 24.06.2030</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>RU000A0DBM5</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="H37" t="n">
         <v>180</v>
       </c>
-      <c r="F37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="I37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J37" t="n">
         <v>17.3</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>24 дек. 2027 г.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Магнит ПАО БО-005P-04 Рейтинг: ААА (АКРА, прогноз «Стабильный») Купон: КС+150 б.п. финальный (ежемесячный) Срок обращения: 2 года Объем: 10 млрд. Р Амортизация: нет Оферта: нет Номинал: 1000 Р</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>RU000A10DDU4</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>99.89</v>
-      </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="H38" t="n">
         <v>10</v>
       </c>
-      <c r="F38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="I38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J38" t="n">
         <v>17</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
-        <v>-0.1099999999999994</v>
-      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Новабев Групп 003Р-02 RU000SYNG3P2 Объем: 3 млрд Р Купон: ФИНАЛ = 15.25% (было до 16% (YTM до 17,23%)) Выплаты: 12 раз в год Срок: 3 года (1080 дней) до 20.01.29 Оферта: нет Рейтинг: АА от ЭкспертРА и НКР Амортизация: 50% от номинала в дату выплаты 30 купона. Сбор заявок - 2 февраля, размещение - 5 февраля 2026.</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>RU000SYNG3P2</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
         <is>
           <t>АА</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="H39" t="n">
         <v>200</v>
       </c>
-      <c r="F39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="I39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J39" t="n">
         <v>15.25</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>ОФЗ 26248. Купон 12.25% Выплата купонов 2 раза в год в июне и декабре по 61.08 руб</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>RU000A108EH4</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="H40" t="n">
         <v>2600</v>
       </c>
-      <c r="F40" t="n">
+      <c r="I40" t="n">
         <v>865.78</v>
       </c>
-      <c r="G40" t="n">
+      <c r="J40" t="n">
         <v>14.149</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>ОФЗ 26250. RU000A10BVH7 . Купон 12%. Выплата купонов 2 раза в год в июне и декабре</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>RU000A10BVH7</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="H41" t="n">
         <v>300</v>
       </c>
-      <c r="F41" t="n">
+      <c r="I41" t="n">
         <v>878.6</v>
       </c>
-      <c r="G41" t="n">
+      <c r="J41" t="n">
         <v>13.658</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>ОФЗ 26253 на 13 лет. Купон 13%. Выплата купонов 2 раза в год в апреле и октябре</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>RU000A10D517</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="H42" t="n">
         <v>1402</v>
       </c>
-      <c r="F42" t="n">
+      <c r="I42" t="n">
         <v>938.29</v>
       </c>
-      <c r="G42" t="n">
+      <c r="J42" t="n">
         <v>13.855</v>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Новабев групп 002Р БО-П07 под кс+1.4% ежм на неполных 2 года. Без оферты и амортизации. Облигации (с рынка)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>RU000A1099A2</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>99.59999999999999</v>
-      </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
         <is>
           <t>А</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="H43" t="n">
         <v>50</v>
       </c>
-      <c r="F43" t="n">
+      <c r="I43" t="n">
         <v>1000.2</v>
       </c>
-      <c r="G43" t="n">
+      <c r="J43" t="n">
         <v>16.897</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
-        <v>-0.4200000000000159</v>
-      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Selectel (Селектел 001P-06R) на 2.5 года под 15.4% (на размещении 15-16.5%) с ежм выплатой. Без оферты и амортизации</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>RU000A10CU89</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>101.76</v>
-      </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
         <is>
           <t>АА-, А+</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="H44" t="n">
         <v>100</v>
       </c>
-      <c r="F44" t="n">
+      <c r="I44" t="n">
         <v>999.2</v>
       </c>
-      <c r="G44" t="n">
+      <c r="J44" t="n">
         <v>15.412</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="n">
-        <v>1.840000000000003</v>
-      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>ЕвразХолдинг 003Р-05 USD на 3 года. Первичное размещение под 8.25% по курсу ЦБ в долларах. Выплата купона каждые 30 дней в рублях по курсу ЦБ. Стоимость одной облигации 100$. Без оферты и амортизации.</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>RU000A10D806</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>100.96</v>
-      </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
         <is>
           <t>АА</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="H45" t="n">
         <v>33</v>
       </c>
-      <c r="F45" t="n">
+      <c r="I45" t="n">
         <v>8126.9</v>
       </c>
-      <c r="G45" t="n">
+      <c r="J45" t="n">
         <v>1.015</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="n">
-        <v>-711.7299999999999</v>
-      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Облигации USD Полипласт П02-БО-06 USD на 2.5 года. Первичное размещение под 12.5-13% по курсу ЦБ в долларах. Выплата купона каждые 30 дней в рублях по курсу ЦБ. Стоимость одной облигации 100$</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>RU000A10BU07</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>101.1</v>
-      </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
         <is>
           <t>А Стабильный</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="H46" t="n">
         <v>6</v>
       </c>
-      <c r="F46" t="n">
+      <c r="I46" t="n">
         <v>7848</v>
       </c>
-      <c r="G46" t="n">
+      <c r="J46" t="n">
         <v>1.65</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="n">
-        <v>-683.6999999999999</v>
-      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>Облигации USD Полипласт П02-БО-09 USD RU000A10CH11 на 2.5 года. Первичное размещение под 11.25% по курсу ЦБ в долларах. Выплата купона каждые 30 дней в рублях по курсу ЦБ. Стоимость одной облигации 100$</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>RU000A10CH11</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>98.94289999999999</v>
-      </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
         <is>
           <t>А Стабильный</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="H47" t="n">
         <v>35</v>
       </c>
-      <c r="F47" t="n">
+      <c r="I47" t="n">
         <v>8010.45</v>
       </c>
-      <c r="G47" t="n">
+      <c r="J47" t="n">
         <v>1.404</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="n">
-        <v>-702.1021</v>
-      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>ВУШ 001Р-04. Whoosh. Купон ФИНАЛ=20.25% (было 21.5-22%) каждые 30 дней, на 3 года. Без оферты и амортизации</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>RU000A10BS76</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>97.20999999999999</v>
-      </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
         <is>
           <t>А- Стабильный</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="H48" t="n">
         <v>223</v>
       </c>
-      <c r="F48" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G48" t="n">
+      <c r="I48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J48" t="n">
         <v>20.25</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="n">
-        <v>-2.790000000000006</v>
-      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>АФК СИСТЕМА 002Р-02 под 22.75% ежм. Без оферты, без амортизации. На 2 года</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>RU000A10BPZ1</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>107.41</v>
-      </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
         <is>
           <t>АА- негативный</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="H49" t="n">
         <v>100</v>
       </c>
-      <c r="F49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G49" t="n">
+      <c r="I49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J49" t="n">
         <v>22.75</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="n">
-        <v>7.409999999999997</v>
-      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>АФК СИСТЕМА 002Р-03. На 1 год и 8 месяцев под 22-22.5%. Размещение 2 июля. Финальная ставка 21.5%</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>RU000A10BY94</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>104.9</v>
-      </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
         <is>
           <t>АА- негативный</t>
         </is>
       </c>
-      <c r="E50" t="n">
+      <c r="H50" t="n">
         <v>300</v>
       </c>
-      <c r="F50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G50" t="n">
+      <c r="I50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J50" t="n">
         <v>21.5</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="n">
-        <v>4.900000000000006</v>
-      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Облигации Атомэнергопром 001Р-07 RU000A10C6L5 с фиксированным купоном 14.35% на 5 лет без оферты и амортизации. Выплата каждый квартал в январе, апреле, июле, октябре</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>RU000A10C6L5</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>100.39</v>
-      </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="H51" t="n">
         <v>222</v>
       </c>
-      <c r="F51" t="n">
+      <c r="I51" t="n">
         <v>991.9</v>
       </c>
-      <c r="G51" t="n">
+      <c r="J51" t="n">
         <v>14.467</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="n">
-        <v>1.200000000000003</v>
-      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Облигации Атомэнергопром 001Р-08 RU000A10CT33 на 5 лет под 14.7% КБД (за 5 лет)+1.5%, без оферты и амортизации. Выплата каждый квартал: в марте, июне, сентябре и декабре.</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>RU000A10CT33</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>101.8</v>
-      </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="H52" t="n">
         <v>150</v>
       </c>
-      <c r="F52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G52" t="n">
+      <c r="I52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J52" t="n">
         <v>14.7</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
-        <v>1.799999999999997</v>
-      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Облигации Аэрофлот П02-БО-02 AFLTP02BO02 RU000A10CS75. под КС+1.6% ежм на 5 лет без оферты и амортизации.</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>RU000A10CS75</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>99.26000000000001</v>
-      </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
         <is>
           <t>АА Стабильный</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="H53" t="n">
         <v>700</v>
       </c>
-      <c r="F53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G53" t="n">
+      <c r="I53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J53" t="n">
         <v>17.1</v>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="n">
-        <v>-0.7399999999999949</v>
-      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Аэрофлот выпуск 1. Купон 8.35% 4 раза в год. Март, июнь, сентябрь, декабрь</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>RU000A103943</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>98.52</v>
-      </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
         <is>
           <t>АА Стабильный</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="H54" t="n">
         <v>3000</v>
       </c>
-      <c r="F54" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="I54" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J54" t="n">
         <v>8.35</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="n">
-        <v>-1.480000000000004</v>
-      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Брусника 002-Р04 на 3 года под 21.5% без амортизации и оферты. Купоны каждые 30 дней. Размещение 8 августа 2025</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>RU000A10C8F3</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>98.20999999999999</v>
-      </c>
-      <c r="C55" t="n">
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
         <v>101</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
         <is>
           <t>А- негативный</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="H55" t="n">
         <v>200</v>
       </c>
-      <c r="F55" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G55" t="n">
+      <c r="I55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J55" t="n">
         <v>21.5</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="n">
-        <v>-1.790000000000006</v>
-      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RU000VTBL1P4</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>Облигации ВТБ Лизинг 001Р-МБ-04 АА RU000VTBL1P4 на 3 года. Первичное размещение под 16.5%. Выплата каждые 30 дней. Амортизация каждые 3 мес по 8%, при завершении ещё 12%. Оферты нет. Размещение 16.12.25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RU000A10DTG9</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
         <is>
           <t>АА Стабильный</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="H56" t="n">
         <v>200</v>
       </c>
-      <c r="F56" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G56" t="n">
+      <c r="I56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J56" t="n">
         <v>16.5</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>ГМК Норникель БО-001P-14-USD под 6.5-7% (финал 6.4%) ежм на 4 года без оферты и амортизации.</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>RU000A10CRC4</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>98.49630000000001</v>
-      </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="H57" t="n">
         <v>169</v>
       </c>
-      <c r="F57" t="n">
+      <c r="I57" t="n">
         <v>8306.43</v>
       </c>
-      <c r="G57" t="n">
+      <c r="J57" t="n">
         <v>0.77</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="n">
-        <v>-732.1467</v>
-      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Гельтек-Медика Б0-01 под 22% на 3 года без амортизации и оферты</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>RU000A10D3G1</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>111.5</v>
-      </c>
-      <c r="C58" t="n">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="n">
         <v>112</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
         <is>
           <t>ВВВ</t>
         </is>
       </c>
-      <c r="E58" t="n">
+      <c r="H58" t="n">
         <v>26</v>
       </c>
-      <c r="F58" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="I58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J58" t="n">
         <v>22</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>ИЭК Холдинг 001Р-04 (А-) на 2 года под КС+2.75% ежм (размещение было до КС+3.25), без амортизации, без оферты. Только для квалиф. инвесторов</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>RU000A10CZ43</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>99.38</v>
-      </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
         <is>
           <t>А-</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="H59" t="n">
         <v>250</v>
       </c>
-      <c r="F59" t="n">
+      <c r="I59" t="n">
         <v>998.98</v>
       </c>
-      <c r="G59" t="n">
+      <c r="J59" t="n">
         <v>18.269</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="n">
-        <v>-0.5180000000000007</v>
-      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>Облигации МСП Факторинг 001Р-01 RU000A10D7Z2 на 2 года под КС+300 (19.5% при КС=16.5%) ЕЖМ без оферты и амортизации. Взял с рынка</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>RU000A10D7Z2</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>100.39</v>
-      </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
         <is>
           <t>АА</t>
         </is>
       </c>
-      <c r="E60" t="n">
+      <c r="H60" t="n">
         <v>508</v>
       </c>
-      <c r="F60" t="n">
+      <c r="I60" t="n">
         <v>1004.5</v>
       </c>
-      <c r="G60" t="n">
+      <c r="J60" t="n">
         <v>18.417</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="n">
-        <v>-0.06000000000000227</v>
-      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>Облигации Новые технологии (А-) Нов Техн-001P-08 RU000A10CMQ5 на 2 года под 18-19% (ФИНАЛ 17%) ежм, без амортизации, без оферты</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>RU000A10CMQ5</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>101.18</v>
-      </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
         <is>
           <t>А-</t>
         </is>
       </c>
-      <c r="E61" t="n">
+      <c r="H61" t="n">
         <v>200</v>
       </c>
-      <c r="F61" t="n">
+      <c r="I61" t="n">
         <v>997.8</v>
       </c>
-      <c r="G61" t="n">
+      <c r="J61" t="n">
         <v>17.037</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="n">
-        <v>1.400000000000006</v>
-      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>ОФЗ 26226. Купон 7.95 в апреле и октябре</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>RU000A0ZZYW2</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E62" t="n">
+      <c r="H62" t="n">
         <v>50</v>
       </c>
-      <c r="F62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G62" t="n">
+      <c r="I62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J62" t="n">
         <v>7.95</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>ОФЗ 26252 на 8 лет. Купон 12.5%. Выплата купонов 2 раза в год в апреле и октябре</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>RU000A10D4Y2</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F63" t="n">
+      <c r="H63" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I63" t="n">
         <v>916.62</v>
       </c>
-      <c r="G63" t="n">
+      <c r="J63" t="n">
         <v>13.637</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>ОФЗ 26254 на 15 лет. Купон 13%. Выплата купонов 2 раза в год в апреле и октябре</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>RU000A10D533</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr">
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="H64" t="n">
         <v>267</v>
       </c>
-      <c r="F64" t="n">
+      <c r="I64" t="n">
         <v>915.39</v>
       </c>
-      <c r="G64" t="n">
+      <c r="J64" t="n">
         <v>14.202</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>ОФЗ 29008. Купонная доходность зависит от RUONIA за 6 месяцев +1.4%. Выплата 2 раза в год. Взял с рынка</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>RU000A0JV4P3</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="H65" t="n">
         <v>700</v>
       </c>
-      <c r="F65" t="n">
+      <c r="I65" t="n">
         <v>1046.02</v>
       </c>
-      <c r="G65" t="n">
+      <c r="J65" t="n">
         <v>19.732</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>ОФЗ 29025. Купонная доходность зависит от RUONIA за 6 месяцев + 0%. Выплата 4 раза в год: февраль, май, август, ноябрь</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>RU000A106Z61</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="H66" t="n">
         <v>100</v>
       </c>
-      <c r="F66" t="n">
+      <c r="I66" t="n">
         <v>945.52</v>
       </c>
-      <c r="G66" t="n">
+      <c r="J66" t="n">
         <v>0</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>Полипласт П02-БО-05 на 2 года. Первичное размещение под 25.5%. Выплата купона каждые 30 дней.</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>RU000A10BPN7</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>109.69</v>
-      </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
         <is>
           <t>А Стабильный</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="H67" t="n">
         <v>500</v>
       </c>
-      <c r="F67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G67" t="n">
+      <c r="I67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J67" t="n">
         <v>25.5</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="n">
-        <v>9.689999999999998</v>
-      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>Облигации Село Зелёное серии 001Р-01 (RU000A10D4W6). На 1.5 года под КС+260 (при сборе заявок и КС=17% была вилка 19.6 - 20%) ежм без амортизации и оферты.</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>RU000A10D4W6</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>100</v>
-      </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr">
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
         <is>
           <t>А</t>
         </is>
       </c>
-      <c r="E68" t="n">
+      <c r="H68" t="n">
         <v>10</v>
       </c>
-      <c r="F68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G68" t="n">
+      <c r="I68" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J68" t="n">
         <v>18.1</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>Облигации Сибур СЕРИИ 001P-08 в USD. На 5 лет под 6.65% (был диапазон 7-7.2%) каждые 30 дней, без амортизации и оферты. Размещение 03.09.25.</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>RU000A10CMR</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="H69" t="n">
         <v>17</v>
       </c>
-      <c r="F69" t="n">
+      <c r="I69" t="n">
         <v>8059.47</v>
       </c>
-      <c r="G69" t="n">
+      <c r="J69" t="n">
         <v>0.825</v>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>Облигации ФосАгро БО-02-04 (RU000A10CZ68) USD под 7-7.25% (7% ФИНАЛ) ежм на 3 года (1106 дней) без оферты и амортизации</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>RU000A10CZ68</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>102.99</v>
-      </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
         <is>
           <t>AAA Стабильный</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="H70" t="n">
         <v>6</v>
       </c>
-      <c r="F70" t="n">
+      <c r="I70" t="n">
         <v>81496.7</v>
       </c>
-      <c r="G70" t="n">
+      <c r="J70" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="n">
-        <v>-8046.68</v>
-      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>Облигации Эфферон 001 Р-01 RU000A10CH03 на 3 года под 22% с выплатой купонов раз в квартал. Без амортизации и оферты</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>RU000A10СНОЗ</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="n">
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="n">
         <v>104.2</v>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
         <is>
           <t>ВВ Стабильный</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="H71" t="n">
         <v>48</v>
       </c>
-      <c r="F71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G71" t="n">
+      <c r="I71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J71" t="n">
         <v>22</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>Группа ЛСР БО 001Р-09. Купил с рынка по цене 96.98% с доходностью к погашению 18.54% с фикс купоном 14.75% ежм. Без амортизации.</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>RU000A1082X0</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>99.2</v>
-      </c>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
         <is>
           <t>А Стабильный</t>
         </is>
       </c>
-      <c r="E72" t="n">
+      <c r="H72" t="n">
         <v>100</v>
       </c>
-      <c r="F72" t="n">
+      <c r="I72" t="n">
         <v>969.8</v>
       </c>
-      <c r="G72" t="n">
+      <c r="J72" t="n">
         <v>15.209</v>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="n">
-        <v>2.220000000000013</v>
-      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>Облигации: Авто Финанс Банк, Б0-001P-17 (4802-17- 00170-B-001P) на 3 года под КС+215 ежм, без оферты и амортизации</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>RU000A10D9L8</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>101.05</v>
-      </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr">
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
         <is>
           <t>АА</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="H73" t="n">
         <v>254</v>
       </c>
-      <c r="F73" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G73" t="n">
+      <c r="I73" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J73" t="n">
         <v>17.65</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="n">
-        <v>1.049999999999997</v>
-      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>ПАО ЮжУралзолото 001Р-04 USD (RU000A10B008). Купоны 10.6% ЕЖМ на 2 года</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>RU000A10B008</t>
         </is>
       </c>
-      <c r="B74" t="n">
-        <v>97.40000000000001</v>
-      </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr">
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
         <is>
           <t>АА</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="H74" t="n">
         <v>15</v>
       </c>
-      <c r="F74" t="n">
+      <c r="I74" t="n">
         <v>8093.93</v>
       </c>
-      <c r="G74" t="n">
+      <c r="J74" t="n">
         <v>1.31</v>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="n">
-        <v>-711.9930000000001</v>
-      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>РеСтор 001Р-02 на 2 года Купон: ФИНАЛ 18.85% (БЫЛО при сборе до 20%) - Выплаты: 12 раз в год - Рейтинг: A-(RU) от АКРА Со стабильным прогнозом - Амортизация: отсутствует - Оферта: отсутствует Погашение 28.11.27</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>RU000A10DMN0</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>101.75</v>
-      </c>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr">
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
         <is>
           <t>А- Стабильный</t>
         </is>
       </c>
-      <c r="E75" t="n">
+      <c r="H75" t="n">
         <v>165</v>
       </c>
-      <c r="F75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G75" t="n">
+      <c r="I75" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J75" t="n">
         <v>18.85</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="n">
-        <v>1.75</v>
-      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>Росагролизинг 002Р-04 под КС+2.2% ежм на 3 года без оферты и амортизации.</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>RU000A10CS91</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>99.23999999999999</v>
-      </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr">
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
         <is>
           <t>АА- Стабильный</t>
         </is>
       </c>
-      <c r="E76" t="n">
+      <c r="H76" t="n">
         <v>100</v>
       </c>
-      <c r="F76" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G76" t="n">
+      <c r="I76" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J76" t="n">
         <v>17.7</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="n">
-        <v>-0.7600000000000051</v>
-      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>СКС Ломбард БО-02 (СКСЛомб-БО-02) под 27% ежм на 3 года (Оферта Колл через 1.5 года - 16.03.27. Погашение 06.09.28. Только для квалифицированных инвесторов) !!! СПЕКУЛЯТИВНО !!!</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>RU000A10CST6</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>103.71</v>
-      </c>
-      <c r="C77" t="n">
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="n">
         <v>104.5</v>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="H77" t="n">
         <v>6</v>
       </c>
-      <c r="F77" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G77" t="n">
+      <c r="I77" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J77" t="n">
         <v>27</v>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>16 мар. 2027 г.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="n">
-        <v>3.709999999999994</v>
-      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>Сбербанк 001P- SberD3 RU000A109X37 Рейтинг: ААА ДИСКОНТНЫЕ ОБЛИГАЦИИ, купон 0% Срок: 3,7 лет Доходность: 15,5% Погашение 12.11.29 Приобретено с рынка 27.02.26 по цене 58.69, что даёт доходность 70.38% за 3.67 лет, или 15.44% годовой ставки. Кроме того, на доход должен действовать ЛДВ, то есть отсутствие налога</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>RU000A109X37</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>60.13</v>
-      </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr">
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="E78" t="n">
+      <c r="H78" t="n">
         <v>200</v>
       </c>
-      <c r="F78" t="n">
+      <c r="I78" t="n">
         <v>586.9</v>
       </c>
-      <c r="G78" t="n">
+      <c r="J78" t="n">
         <v>0</v>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="n">
-        <v>1.440000000000005</v>
-      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>Сбер 1P51 (фикс) Cбep-001P-SBER51 Купон: до 14,85% (YTM до 15,91%) Выплаты: 12 раз в год Срок: 2,5 лет (913 дней) до 16.06.28 Оферта: нет Амортизация: нет Выпуск для всех Кредитный рейтинг: ААА "стабильный" от АКРА (май 2025) и НКР (октябрь 2025).</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>RU000A10DS74</t>
         </is>
       </c>
-      <c r="B79" t="n">
-        <v>101.95</v>
-      </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr">
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E79" t="n">
+      <c r="H79" t="n">
         <v>350</v>
       </c>
-      <c r="F79" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G79" t="n">
+      <c r="I79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J79" t="n">
         <v>14.85</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="n">
-        <v>1.950000000000003</v>
-      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>Селектел 001P-07R: • Рейтинг: АА- (Эксперт РА, прогноз «Стабильный») • Номинал: 1000Р Объем: 5 млрд рублей Срок обращения: 3 года • Купон: ФИНАЛ 15%, было не выше 16,60% годовых (УТМ не выше 17,92% годовых) • Периодичность выплат: ежемесячно • Амортизация: отсутствует Оферта: отсутствует Квал: не требуется • Сбор заявок: 27 февраля 2026 • Дата размещения: 04 марта 2026 года Погашение 16.02.29</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>RU000A10EEZ9</t>
         </is>
       </c>
-      <c r="B80" t="n">
-        <v>101.3</v>
-      </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr">
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
         <is>
           <t>АА-, А+</t>
         </is>
       </c>
-      <c r="E80" t="n">
+      <c r="H80" t="n">
         <v>100</v>
       </c>
-      <c r="F80" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G80" t="n">
+      <c r="I80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J80" t="n">
         <v>15</v>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="n">
-        <v>1.299999999999997</v>
-      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>Селигдар 001Р-07, RU000A10D3X6 КС+450 б.п., без оферты и амортизации на 2 года. Взял с рынка по цене 1003.68 руб</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>RU000A10D3X6</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>100.76</v>
-      </c>
-      <c r="C81" t="n">
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="n">
         <v>103.5</v>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
         <is>
           <t>А+</t>
         </is>
       </c>
-      <c r="E81" t="n">
+      <c r="H81" t="n">
         <v>200</v>
       </c>
-      <c r="F81" t="n">
+      <c r="I81" t="n">
         <v>1003.68</v>
       </c>
-      <c r="G81" t="n">
+      <c r="J81" t="n">
         <v>19.927</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="n">
-        <v>0.3920000000000101</v>
-      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>СелоЗел-001P-02 RU000A10DQ68 Рейтинг: А (НКР, прогноз «Стабильный») Купон: ФИНАЛ 17.25. Сбор заявок был с купоном до 18.00% (ежемесячный) Срок обращения: 2 года, до 25.11.27 Амортизация: нет Оферта: нет</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>RU000A10DQ68</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>102.21</v>
-      </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr">
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
         <is>
           <t>А</t>
         </is>
       </c>
-      <c r="E82" t="n">
+      <c r="H82" t="n">
         <v>210</v>
       </c>
-      <c r="F82" t="n">
+      <c r="I82" t="n">
         <v>995</v>
       </c>
-      <c r="G82" t="n">
+      <c r="J82" t="n">
         <v>17.337</v>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="n">
-        <v>2.709999999999994</v>
-      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>Сибур 001Р-09 объем: $150 млн номинал: $100 купон: ФИНАЛ = 7.5% (было до 7,75) (ежемесячный) Годовых доходность: до 8,03% срок: 3 года (1110 дней= 06.03.29 ???) амортизация/оферта: нет рейтинг эмитента: AAA(RU) от АКРА, ruAAA от Эксперт РА доступно: всем сбор заявок: 18.02.26 Размещение 20.02.26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>RU000A10ECK5</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>101</v>
-      </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr">
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E83" t="n">
+      <c r="H83" t="n">
         <v>10</v>
       </c>
-      <c r="F83" t="n">
+      <c r="I83" t="n">
         <v>7664.05</v>
       </c>
-      <c r="G83" t="n">
+      <c r="J83" t="n">
         <v>0.979</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="n">
-        <v>-665.405</v>
-      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>Софтлайн 002P-02 - Купон: фиксированный, ФИНАЛ 19.5% (был ориентир до 20,50%) - Выплаты: ежемесячно (12 раз в год) - Погашение: 2 года 10 месяцев (1041 день) = 20.12.28 - Рейтинг: BBB+ (позитивный) от Эксперт РА - Амортизация: нет Оферта: нет - Объем выпуска: от 3 млрд руб. - Прием заявок: 10 февраля 2026, размещение 13 февраля 2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>RU000A10EA08</t>
         </is>
       </c>
-      <c r="B84" t="n">
-        <v>103.9</v>
-      </c>
-      <c r="C84" t="n">
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="n">
         <v>107</v>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
         <is>
           <t>ВВВ+</t>
         </is>
       </c>
-      <c r="E84" t="n">
+      <c r="H84" t="n">
         <v>200</v>
       </c>
-      <c r="F84" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G84" t="n">
+      <c r="I84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J84" t="n">
         <v>19.5</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="n">
-        <v>3.900000000000006</v>
-      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>ТОМСКАЯ область. Томско6-34076 Рейтинг: BBB+ (Эксперт РА, прогноз «Стабильный») Купон: Финал 16.0% фикс, квартальный в марте, июне, сентябре и декабре. (Было КБД (3.2 года) +400 б.п. (фикс ориентировочно до 17.2%)) Срок обращения: 5 лет Объем: 5 млрд. Р Амортизация: да (16, 20 купоны по 50%) Оферта: нет Номинал: 1000 Р Сбор заявок 16 декабря 11:00-14:00 размещение 18 декабря 2025</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>RU000A10DWQ2</t>
         </is>
       </c>
-      <c r="B85" t="n">
-        <v>103.7</v>
-      </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr">
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
         <is>
           <t>ВВВ+</t>
         </is>
       </c>
-      <c r="E85" t="n">
+      <c r="H85" t="n">
         <v>52</v>
       </c>
-      <c r="F85" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G85" t="n">
+      <c r="I85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J85" t="n">
         <v>16</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="n">
-        <v>3.700000000000003</v>
-      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>Томская область 34075 Ставка купона: КБД за 2.1 года + 5%. ФИНАЛ = 16.2%. Срок обращения: 3,1 года. Дюрация: 2,1 года Купон: 12 раз в год Рейтинг: BBB+ Амортизация: 40% – 25 купон, 60% – 37 купон Оферта: нет Дата размещения: 14.11.25</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>RU000A10DEN7</t>
         </is>
       </c>
-      <c r="B86" t="n">
-        <v>102.48</v>
-      </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
         <is>
           <t>ВВВ+</t>
         </is>
       </c>
-      <c r="E86" t="n">
+      <c r="H86" t="n">
         <v>50</v>
       </c>
-      <c r="F86" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G86" t="n">
+      <c r="I86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J86" t="n">
         <v>16.2</v>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="n">
-        <v>2.480000000000004</v>
-      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>ФСК Россети-001P-19R FSKE001P19R RU000A10DM96 Погашение: через 2,8 года до 13.09.2028 Купон: КС +130 б.п. (При размещении КС+155) Выплаты: 12 раз в год Амортизация: Нет Оферта: Нет Рейтинг: AAA(RU) АКРА / ruAAA Эксперт РА</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>RU000A10DM96</t>
         </is>
       </c>
-      <c r="B87" t="n">
-        <v>100.2</v>
-      </c>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr">
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E87" t="n">
+      <c r="H87" t="n">
         <v>200</v>
       </c>
-      <c r="F87" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G87" t="n">
+      <c r="I87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J87" t="n">
         <v>16.8</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="n">
-        <v>0.2000000000000028</v>
-      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>Федеральная пассажирская компания АО «ФПК» 002P-01 RU000A10DYC8 Рейтинг: АА+, прогноз «стабильный» (НРА) Купон: ФИНАЛ 15.4 фикс. (КБД (2,5 года)+275 б.п., это до 15.9%), ежемесячный Срок: 2,5 года Объем: 30 млрд руб. Амортизация: нет Оферта: нет Номинал: 1000 руб. - Доступен неквал. инвесторам Дата размещения: 23 декабря</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>RU000A10DYC8</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>102.38</v>
-      </c>
       <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr">
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
         <is>
           <t>АА+</t>
         </is>
       </c>
-      <c r="E88" t="n">
+      <c r="H88" t="n">
         <v>400</v>
       </c>
-      <c r="F88" t="n">
+      <c r="I88" t="n">
         <v>995</v>
       </c>
-      <c r="G88" t="n">
+      <c r="J88" t="n">
         <v>15.477</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="n">
-        <v>2.879999999999995</v>
-      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>МКПАО Яндекс 001Р-03 - Купон: Ключевая ставка ЦБ + 1,45% (флоатер) - Выплаты: 12 раз в год (ежемесячно) - Погашение: Через 3 года - Рейтинг: ААА Амортизация: отсутствует - Оферта: отсутствует - Прием заявок: 13 ноября 2025, размещение 18 ноября</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>RU000A10DDR0</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>100.14</v>
-      </c>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr">
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
         <is>
           <t>ААА</t>
         </is>
       </c>
-      <c r="E89" t="n">
+      <c r="H89" t="n">
         <v>200</v>
       </c>
-      <c r="F89" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G89" t="n">
+      <c r="I89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J89" t="n">
         <v>16.95</v>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="n">
-        <v>0.1400000000000006</v>
-      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>Эмитент: ООО «ИЛОН» Илон-001P-01 RU000A10EG44 - Купон: ФИНАЛ 17.7%. было Не выше 20,00% годовых (YTM до 21,94%). - Выплаты: Ежемесячно - Погашение: 2 года (720 дней) - Рейтинг: BBB+(RU), позитивный прогноз от AKPA (09.10.2025). - Амортизация: нет - Оферта: Отсутствует. - Объем выпуска: 1 млрд руб. - Прием заявок: До 03 марта 2026 г. Размещение 06.03.26 Дата погашения: 24.02.2028</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>RU000A10EG44</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>101.9</v>
-      </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr">
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
         <is>
           <t>BBB+</t>
         </is>
       </c>
-      <c r="E90" t="n">
+      <c r="H90" t="n">
         <v>86</v>
       </c>
-      <c r="F90" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G90" t="n">
+      <c r="I90" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J90" t="n">
         <v>17.7</v>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="n">
-        <v>1.900000000000006</v>
-      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Bonds/bond_report.xlsx
+++ b/Bonds/bond_report.xlsx
@@ -494,7 +494,9 @@
           <t>RU000A10E7W8</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>99.90000000000001</v>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -514,7 +516,9 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>-0.09999999999999432</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -527,7 +531,9 @@
           <t>RU000A10EHB3</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>101.48</v>
+      </c>
       <c r="D3" t="n">
         <v>103.5</v>
       </c>
@@ -557,7 +563,9 @@
           <t>да</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>1.480000000000004</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -570,7 +578,9 @@
           <t>RU000A10DZU7</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>101.91</v>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -590,7 +600,9 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>1.909999999999997</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -603,7 +615,9 @@
           <t>RU000A10DZT9</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>101.43</v>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -623,7 +637,9 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>1.430000000000007</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -636,7 +652,9 @@
           <t>RU000A109SH2</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>100.02</v>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -656,7 +674,9 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>-0.04000000000000625</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -669,7 +689,9 @@
           <t>RU000A109L49</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>99.55</v>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -689,7 +711,9 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>-0.2700000000000102</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -702,7 +726,9 @@
           <t>RU000A10DSL1</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>101.57</v>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -726,7 +752,9 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>1.569999999999993</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +767,9 @@
           <t>RU000A10E5C4</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>100.5</v>
+      </c>
       <c r="D9" t="n">
         <v>103.5</v>
       </c>
@@ -765,7 +795,9 @@
           <t>да</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -778,7 +810,9 @@
           <t>RU000A10CU55</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>98.7</v>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -798,7 +832,9 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>-0.75</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +847,9 @@
           <t>RU000A10E4Y1</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>104.09</v>
+      </c>
       <c r="D11" t="n">
         <v>103.5</v>
       </c>
@@ -837,7 +875,9 @@
           <t>да</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>4.090000000000003</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -908,7 +948,9 @@
           <t>RU000A10DYG9</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>103.49</v>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -928,7 +970,9 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>3.489999999999995</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -941,7 +985,9 @@
           <t>RU000A10EJQ7</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>100.66</v>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -961,7 +1007,9 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0.6599999999999966</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -974,7 +1022,9 @@
           <t>RU000A10DPS2</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>103.15</v>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -994,7 +1044,9 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>3.150000000000006</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1007,7 +1059,9 @@
           <t>RU000A10BJX9</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>103.76</v>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -1027,7 +1081,9 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>3.760000000000005</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1077,7 +1133,9 @@
           <t>RU000A10CQE2</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>100.28</v>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -1097,7 +1155,9 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>16.88</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1110,7 +1170,9 @@
           <t>RU000A10CTX6</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>100.1095</v>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -1130,7 +1192,9 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>-8260.580499999998</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1143,7 +1207,9 @@
           <t>RU000A105YH8</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>98.04000000000001</v>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
@@ -1163,7 +1229,9 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>-0.769999999999996</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1176,7 +1244,9 @@
           <t>RU000A10EA40</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>101.93</v>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
@@ -1200,7 +1270,9 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>1.930000000000007</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1213,7 +1285,9 @@
           <t>RU000A10EHJ6</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>100.56</v>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -1233,7 +1307,9 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0.5600000000000023</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1246,7 +1322,9 @@
           <t>RU000A10EAM5</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>102.2469</v>
+      </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
@@ -1266,7 +1344,9 @@
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>-663.9541</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1279,7 +1359,9 @@
           <t>RU000A10D2Q2</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="n">
+        <v>100.17</v>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
@@ -1299,7 +1381,9 @@
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0.1700000000000017</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1312,7 +1396,9 @@
           <t>RU000A10D483</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>101.29</v>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
@@ -1332,7 +1418,9 @@
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>-7782.61</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1345,7 +1433,9 @@
           <t>RU000A10DA66</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="n">
+        <v>99.79000000000001</v>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
@@ -1365,7 +1455,9 @@
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>-0.2099999999999937</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1378,7 +1470,9 @@
           <t>RU000A10BK09</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="n">
+        <v>100.4</v>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
@@ -1398,7 +1492,9 @@
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>-0.4749999999999943</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1411,7 +1507,9 @@
           <t>RU000A10E655</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="n">
+        <v>103.64</v>
+      </c>
       <c r="D29" t="n">
         <v>104.5</v>
       </c>
@@ -1433,7 +1531,9 @@
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>3.640000000000001</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1446,7 +1546,9 @@
           <t>RU000A10CKY3</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>100.5</v>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
@@ -1466,7 +1568,9 @@
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>0.8940000000000055</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1479,7 +1583,9 @@
           <t>RU000A10DHT7</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>102.18</v>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -1499,7 +1605,9 @@
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>2.490000000000009</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1570,7 +1678,9 @@
           <t>RU000A10DMS9</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>100.28</v>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
@@ -1590,7 +1700,9 @@
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>0.2800000000000011</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1603,7 +1715,9 @@
           <t>RU000A10DHX9</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="n">
+        <v>102.7</v>
+      </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
@@ -1623,7 +1737,9 @@
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>2.700000000000003</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1636,7 +1752,9 @@
           <t>RU000A10DHV3</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>100.01</v>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -1656,7 +1774,9 @@
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>-0.09999999999999432</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1706,7 +1826,9 @@
           <t>RU000A10DDU4</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="n">
+        <v>99.67</v>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -1726,7 +1848,9 @@
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>-0.3299999999999983</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1871,7 +1995,9 @@
           <t>RU000A1099A2</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="n">
+        <v>99.44</v>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -1891,7 +2017,9 @@
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="n">
+        <v>-0.5800000000000125</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1904,7 +2032,9 @@
           <t>RU000A10CU89</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="n">
+        <v>101.94</v>
+      </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
@@ -1924,7 +2054,9 @@
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="n">
+        <v>2.019999999999996</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1937,7 +2069,9 @@
           <t>RU000A10D806</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="n">
+        <v>101.489</v>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
@@ -1957,7 +2091,9 @@
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>-711.2009999999999</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1970,7 +2106,9 @@
           <t>RU000A10BU07</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="n">
+        <v>100.4737</v>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
@@ -1990,7 +2128,9 @@
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="n">
+        <v>-684.3262999999999</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2003,7 +2143,9 @@
           <t>RU000A10CH11</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="n">
+        <v>98.5977</v>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
@@ -2023,7 +2165,9 @@
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>-702.4472999999999</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2036,7 +2180,9 @@
           <t>RU000A10BS76</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="n">
+        <v>97.47</v>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
@@ -2056,7 +2202,9 @@
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>-2.530000000000001</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2069,7 +2217,9 @@
           <t>RU000A10BPZ1</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="n">
+        <v>107.75</v>
+      </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
@@ -2089,7 +2239,9 @@
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="n">
+        <v>7.75</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2102,7 +2254,9 @@
           <t>RU000A10BY94</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="n">
+        <v>104.7</v>
+      </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
@@ -2122,7 +2276,9 @@
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>4.700000000000003</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2135,7 +2291,9 @@
           <t>RU000A10C6L5</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="n">
+        <v>100.1</v>
+      </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
@@ -2155,7 +2313,9 @@
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>0.9099999999999966</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2168,7 +2328,9 @@
           <t>RU000A10CT33</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="n">
+        <v>101.83</v>
+      </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
@@ -2188,7 +2350,9 @@
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="n">
+        <v>1.829999999999998</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2201,7 +2365,9 @@
           <t>RU000A10CS75</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="n">
+        <v>99.38</v>
+      </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
@@ -2221,7 +2387,9 @@
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="n">
+        <v>-0.6200000000000045</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2234,7 +2402,9 @@
           <t>RU000A103943</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="n">
+        <v>98.45</v>
+      </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
@@ -2254,7 +2424,9 @@
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="n">
+        <v>-1.549999999999997</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2267,7 +2439,9 @@
           <t>RU000A10C8F3</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="n">
+        <v>98.45</v>
+      </c>
       <c r="D55" t="n">
         <v>101</v>
       </c>
@@ -2289,7 +2463,9 @@
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="M55" t="n">
+        <v>-1.549999999999997</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2302,7 +2478,9 @@
           <t>RU000A10DTG9</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="n">
+        <v>101.7</v>
+      </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
@@ -2322,7 +2500,9 @@
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="n">
+        <v>1.700000000000003</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2335,7 +2515,9 @@
           <t>RU000A10CRC4</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="n">
+        <v>98.825</v>
+      </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
@@ -2355,7 +2537,9 @@
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="n">
+        <v>-731.818</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2368,7 +2552,9 @@
           <t>RU000A10D3G1</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>112.5</v>
+      </c>
       <c r="D58" t="n">
         <v>112</v>
       </c>
@@ -2390,7 +2576,9 @@
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2403,7 +2591,9 @@
           <t>RU000A10CZ43</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="n">
+        <v>99.23999999999999</v>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
@@ -2423,7 +2613,9 @@
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="n">
+        <v>-0.6580000000000013</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2436,7 +2628,9 @@
           <t>RU000A10D7Z2</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
+      <c r="C60" t="n">
+        <v>100.27</v>
+      </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
@@ -2456,7 +2650,9 @@
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" t="n">
+        <v>-0.1800000000000068</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2469,7 +2665,9 @@
           <t>RU000A10CMQ5</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="n">
+        <v>101.34</v>
+      </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
@@ -2489,7 +2687,9 @@
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" t="n">
+        <v>1.560000000000002</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2667,7 +2867,9 @@
           <t>RU000A10BPN7</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="n">
+        <v>109.64</v>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
@@ -2687,7 +2889,9 @@
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="n">
+        <v>9.640000000000001</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2700,7 +2904,9 @@
           <t>RU000A10D4W6</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
+      <c r="C68" t="n">
+        <v>100.17</v>
+      </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
@@ -2720,7 +2926,9 @@
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="n">
+        <v>0.1700000000000017</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2766,7 +2974,9 @@
           <t>RU000A10CZ68</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
+      <c r="C70" t="n">
+        <v>100.0674</v>
+      </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
@@ -2786,7 +2996,9 @@
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" t="n">
+        <v>-8049.6026</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2834,7 +3046,9 @@
           <t>RU000A1082X0</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="n">
+        <v>98.45</v>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
@@ -2854,7 +3068,9 @@
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" t="n">
+        <v>1.470000000000013</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2867,7 +3083,9 @@
           <t>RU000A10D9L8</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
+      <c r="C73" t="n">
+        <v>100.92</v>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
@@ -2887,7 +3105,9 @@
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+      <c r="M73" t="n">
+        <v>0.9200000000000017</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2900,7 +3120,9 @@
           <t>RU000A10B008</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
+      <c r="C74" t="n">
+        <v>98</v>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
@@ -2920,7 +3142,9 @@
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="M74" t="n">
+        <v>-711.393</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2933,7 +3157,9 @@
           <t>RU000A10DMN0</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
+      <c r="C75" t="n">
+        <v>103.04</v>
+      </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
@@ -2953,7 +3179,9 @@
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+      <c r="M75" t="n">
+        <v>3.040000000000006</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2966,7 +3194,9 @@
           <t>RU000A10CS91</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
+      <c r="C76" t="n">
+        <v>99.13</v>
+      </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
@@ -2986,7 +3216,9 @@
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+      <c r="M76" t="n">
+        <v>-0.8700000000000045</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2999,7 +3231,9 @@
           <t>RU000A10CST6</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
+      <c r="C77" t="n">
+        <v>104.02</v>
+      </c>
       <c r="D77" t="n">
         <v>104.5</v>
       </c>
@@ -3025,7 +3259,9 @@
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
+      <c r="M77" t="n">
+        <v>4.019999999999996</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3038,7 +3274,9 @@
           <t>RU000A109X37</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="n">
+        <v>60.1</v>
+      </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
@@ -3058,7 +3296,9 @@
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
+      <c r="M78" t="n">
+        <v>1.410000000000004</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3071,7 +3311,9 @@
           <t>RU000A10DS74</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
+      <c r="C79" t="n">
+        <v>102.36</v>
+      </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
@@ -3091,7 +3333,9 @@
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
+      <c r="M79" t="n">
+        <v>2.359999999999999</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3104,7 +3348,9 @@
           <t>RU000A10EEZ9</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
+      <c r="C80" t="n">
+        <v>101.29</v>
+      </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
@@ -3124,7 +3370,9 @@
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
+      <c r="M80" t="n">
+        <v>1.290000000000006</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3137,7 +3385,9 @@
           <t>RU000A10D3X6</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
+      <c r="C81" t="n">
+        <v>100.7</v>
+      </c>
       <c r="D81" t="n">
         <v>103.5</v>
       </c>
@@ -3159,7 +3409,9 @@
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
+      <c r="M81" t="n">
+        <v>0.3320000000000078</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3172,7 +3424,9 @@
           <t>RU000A10DQ68</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
+      <c r="C82" t="n">
+        <v>102.1</v>
+      </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
@@ -3192,7 +3446,9 @@
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
+      <c r="M82" t="n">
+        <v>2.599999999999994</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3205,7 +3461,9 @@
           <t>RU000A10ECK5</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
+      <c r="C83" t="n">
+        <v>102.1995</v>
+      </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
@@ -3225,7 +3483,9 @@
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
+      <c r="M83" t="n">
+        <v>-664.2055</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3238,7 +3498,9 @@
           <t>RU000A10EA08</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
+      <c r="C84" t="n">
+        <v>103.75</v>
+      </c>
       <c r="D84" t="n">
         <v>107</v>
       </c>
@@ -3260,7 +3522,9 @@
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
+      <c r="M84" t="n">
+        <v>3.75</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3273,7 +3537,9 @@
           <t>RU000A10DWQ2</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
+      <c r="C85" t="n">
+        <v>103.94</v>
+      </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
@@ -3293,7 +3559,9 @@
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
+      <c r="M85" t="n">
+        <v>3.939999999999998</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3306,7 +3574,9 @@
           <t>RU000A10DEN7</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
+      <c r="C86" t="n">
+        <v>103.3</v>
+      </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
@@ -3326,7 +3596,9 @@
       </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
+      <c r="M86" t="n">
+        <v>3.299999999999997</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3339,7 +3611,9 @@
           <t>RU000A10DM96</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
+      <c r="C87" t="n">
+        <v>100.4</v>
+      </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
@@ -3359,7 +3633,9 @@
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
+      <c r="M87" t="n">
+        <v>0.4000000000000057</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3372,7 +3648,9 @@
           <t>RU000A10DYC8</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
+      <c r="C88" t="n">
+        <v>102.4</v>
+      </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
@@ -3392,7 +3670,9 @@
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>2.900000000000006</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3405,7 +3685,9 @@
           <t>RU000A10DDR0</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
+      <c r="C89" t="n">
+        <v>100</v>
+      </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
@@ -3425,7 +3707,9 @@
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3438,7 +3722,9 @@
           <t>RU000A10EG44</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
+      <c r="C90" t="n">
+        <v>101.95</v>
+      </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
@@ -3458,7 +3744,9 @@
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
+      <c r="M90" t="n">
+        <v>1.950000000000003</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
